--- a/PCB/produzione/FilMachine_Mainboard_BOM_leggibile.xlsx
+++ b/PCB/produzione/FilMachine_Mainboard_BOM_leggibile.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non montati" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2641,33 +2642,92 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>NON MONTATI (DNP, non sono nella BOM JLCPCB):</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>J6,R6,R7</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Designator</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C6 UART</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DNP: non montato, non e' nella BOM/CPL JLCPCB. Accesso ESP32-C6 (non montato)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4.7k</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DNP: non montato, non e' nella BOM/CPL JLCPCB. Pull-up I2C (non montata: c'e' gia' 2k2 sul display)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4.7k</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DNP: non montato, non e' nella BOM/CPL JLCPCB. Pull-up I2C (non montata)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PCB/produzione/FilMachine_Mainboard_BOM_leggibile.xlsx
+++ b/PCB/produzione/FilMachine_Mainboard_BOM_leggibile.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -724,11 +724,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C20,C21,C22,C23,C24,C25,C26,C27,C28,C29,C54,C61</t>
+          <t>C20,C21,C22,C23,C54,C61</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,11 +1044,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D6,D7,D10,D11,D12,D13,D14,D15,D16,D17,D18,D19,D47,D48</t>
+          <t>D6,D7,D10,D11,D12,D13,D47,D48,D49,D50,D51,D52</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1524,16 +1524,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>J7,J8,J9,J10</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BATH LEVEL / CHEM 1 / CHEM 2 / CHEM 3</t>
+          <t>BATH LEVEL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1703,22 +1703,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>PZ254V-11-05P</t>
+          <t>PZ254V-11-09P</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>C492404</t>
+          <t>C492408</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>PinHeader_1x05_P2.54mm_Vertical</t>
+          <t>PinHeader_1x09_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Header 2,54: A6, A7 (GPIO liberi MCP23017, 3,3 V, tramite 1k + clamp), +3V3, +5V di servizio (PTC F5), GND</t>
+          <t>Header 2,54: B0-B5 (GPIO liberi MCP23017, 3,3 V, tramite 1k + clamp), +3V3, +5V di servizio (PTC F5), GND</t>
         </is>
       </c>
     </row>
@@ -1844,11 +1844,11 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>R1,R9,R41,R42,R43,R44,R45,R46,R61,R62,R70,R71,R72,R73,R74,R75,R76</t>
+          <t>R1,R9,R41,R42,R43,R44,R45,R46,R47,R48,R61,R62,R70,R71,R72,R73,R74,R75,R76</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1964,11 +1964,11 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>R4,R5,R84,R97,R98</t>
+          <t>R4,R5,R84,R97,R98,R99,R100,R101,R102</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2004,11 +2004,11 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>R8,R12,R13,R14,R20,R21,R22,R23,R24,R25,R26,R27,R28,R29,R64,R66,R80,R82</t>
+          <t>R8,R12,R13,R14,R20,R21,R22,R23,R64,R66,R80,R82</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>R47,R48</t>
+          <t>R63,R65</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0603 1M 1%</t>
+          <t>0603 10R 1%</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>C22935</t>
+          <t>C22859</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Pull-down gate uscita spare SP1 (spenta al boot)</t>
+          <t>Gate riscaldatore 1</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>R63,R65</t>
+          <t>R85,R88</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>1.5k</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0603 10R 1%</t>
+          <t>0603 1.5k 1%</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>C22859</t>
+          <t>C22843</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2238,22 +2238,22 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Gate riscaldatore 1</t>
+          <t>Sense IS lato A: kILIS 10000 -&gt; 6 A = 0,8 mA = 1,2 V (10 A = 1,8 V)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>R85,R88</t>
+          <t>R86</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>1.5k</t>
+          <t>30k</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0603 1.5k 1%</t>
+          <t>0603 30k 1%</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>C22843</t>
+          <t>C22984</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Sense IS lato A: kILIS 10000 -&gt; 6 A = 0,8 mA = 1,2 V (10 A = 1,8 V)</t>
+          <t>ILIM: 64 kV / 30k = 2,1 A</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>R86</t>
+          <t>R87</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>30k</t>
+          <t>220R</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0603 30k 1%</t>
+          <t>0603 220R 1%</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>C22984</t>
+          <t>C22962</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>ILIM: 64 kV / 30k = 2,1 A</t>
+          <t>Serie segnale servo</t>
         </is>
       </c>
     </row>
@@ -2328,37 +2328,37 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>R87</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>220R</t>
+          <t>LMR33630ADDA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0603 220R 1%</t>
+          <t>LMR33630ADDAR</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>C22962</t>
+          <t>C841384</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>TI_SO-PowerPAD-8_ThermalVias</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Serie segnale servo</t>
+          <t>Buck sincrono 3,8–36 V -&gt; 5 V 3 A</t>
         </is>
       </c>
     </row>
@@ -2368,37 +2368,37 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>LMR33630ADDA</t>
+          <t>MCP23017-E/SS</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Microchip</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>LMR33630ADDAR</t>
+          <t>MCP23017T-E/SS</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>C841384</t>
+          <t>C558584</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>TI_SO-PowerPAD-8_ThermalVias</t>
+          <t>SSOP-28_5.3x10.2mm_P0.65mm</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Buck sincrono 3,8–36 V -&gt; 5 V 3 A</t>
+          <t>Espansore I2C 16 I/O, indirizzo 0x20</t>
         </is>
       </c>
     </row>
@@ -2408,37 +2408,37 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>MCP23017-E/SS</t>
+          <t>ADS1115</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Microchip</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MCP23017T-E/SS</t>
+          <t>ADS1115IDGSR</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>C558584</t>
+          <t>C37593</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>SSOP-28_5.3x10.2mm_P0.65mm</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Espansore I2C 16 I/O, indirizzo 0x20</t>
+          <t>ADC I2C 16 bit @0x48: AIN0 12 V, AIN1 5 V, AIN2/AIN3 corrente pompa lato A/B</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>ADS1115</t>
+          <t>UCC27524D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2463,37 +2463,37 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ADS1115IDGSR</t>
+          <t>UCC27524DR</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>C37593</t>
+          <t>C465729</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>ADC I2C 16 bit @0x48: AIN0 12 V, AIN1 5 V, AIN2/AIN3 corrente pompa lato A/B</t>
+          <t>Gate driver doppio low-side (ingressi 3,3 V, uscite 12 V); EN interni a pull-up</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U6,U7</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UCC27524D</t>
+          <t>74LVC2G08</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2503,22 +2503,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>UCC27524DR</t>
+          <t>SN74LVC2G08DCTR</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>C465729</t>
+          <t>C352973</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>SSOP-8_2.95x2.8mm_P0.65mm</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Gate driver doppio low-side (ingressi 3,3 V, uscite 12 V); EN interni a pull-up</t>
+          <t>AND: IN1·ENA, IN2·ENA pompa</t>
         </is>
       </c>
     </row>
@@ -2528,115 +2528,75 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U6,U7</t>
+          <t>U8,U9</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>74LVC2G08</t>
+          <t>BTN8962TA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>SN74LVC2G08DCTR</t>
+          <t>BTN8962TAAUMA1</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>C352973</t>
+          <t>C112630</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>SSOP-8_2.95x2.8mm_P0.65mm</t>
+          <t>TO-263-7_TabPin8</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>AND: IN1·ENA, IN2·ENA pompa</t>
+          <t>Mezzo ponte pompa lato A (30 A, 14 mOhm); SR a GND = slew rate massimo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>U8,U9</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>BTN8962TA</t>
+          <t>DRV8871DDA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>BTN8962TAAUMA1</t>
+          <t>DRV8871DDAR</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>C112630</t>
+          <t>C75864</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>TO-263-7_TabPin8</t>
+          <t>TI_SO-PowerPAD-8_ThermalVias</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Mezzo ponte pompa lato A (30 A, 14 mOhm); SR a GND = slew rate massimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>DRV8871DDA</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>DRV8871DDAR</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>C75864</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>TI_SO-PowerPAD-8_ThermalVias</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Ponte H motore spirale 3,6 A picco</t>
         </is>

--- a/PCB/produzione/FilMachine_Mainboard_BOM_leggibile.xlsx
+++ b/PCB/produzione/FilMachine_Mainboard_BOM_leggibile.xlsx
@@ -1924,11 +1924,11 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>R3,R16,R51,R52,R53,R54,R55,R56,R57,R58,R67,R68</t>
+          <t>R3,R16,R51,R52,R53,R54,R55,R56,R57,R58,R67,R68,R80,R82</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2004,11 +2004,11 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>R8,R12,R13,R14,R20,R21,R22,R23,R64,R66,R80,R82</t>
+          <t>R8,R12,R13,R14,R20,R21,R22,R23,R64,R66</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
